--- a/templates/opening-grey-stock-template.xlsx
+++ b/templates/opening-grey-stock-template.xlsx
@@ -28,32 +28,39 @@
     <comment ref="B1" authorId="0">
       <text>
         <r>
-          <t>L-76 or L-75</t>
+          <t>Needed when the quality has more than one specification (see Lists)</t>
         </r>
       </text>
     </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
-          <t>Up to 2 decimals</t>
+          <t>L-76 or L-75</t>
         </r>
       </text>
     </comment>
     <comment ref="D1" authorId="0">
       <text>
         <r>
-          <t>Up to 3 decimals</t>
+          <t>Up to 2 decimals</t>
         </r>
       </text>
     </comment>
     <comment ref="E1" authorId="0">
       <text>
         <r>
+          <t>Up to 3 decimals</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0">
+      <text>
+        <r>
           <t>DD-MM-YYYY; blank = today</t>
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0">
+    <comment ref="G1" authorId="0">
       <text>
         <r>
           <t>Optional</t>
@@ -65,11 +72,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="26">
   <si>
     <t>Fabric Quality</t>
   </si>
   <si>
+    <t>Specification ID</t>
+  </si>
+  <si>
     <t>Factory</t>
   </si>
   <si>
@@ -85,21 +95,33 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>of Fabric Quality</t>
+  </si>
+  <si>
     <t>Mono White</t>
   </si>
   <si>
     <t>L-76</t>
   </si>
   <si>
+    <t>MONOWHITE-S1</t>
+  </si>
+  <si>
     <t>White/Black</t>
   </si>
   <si>
     <t>L-75</t>
   </si>
   <si>
+    <t>WHITEBLACK-S1</t>
+  </si>
+  <si>
     <t>Green Shade Net</t>
   </si>
   <si>
+    <t>GREENSHADENET-S1</t>
+  </si>
+  <si>
     <t>Opening grey stock</t>
   </si>
   <si>
@@ -110,6 +132,9 @@
   </si>
   <si>
     <t>Required. Exactly as in the Lists sheet</t>
+  </si>
+  <si>
+    <t>Needed when the quality has more than one specification (see Lists)</t>
   </si>
   <si>
     <t>Required. L-76 or L-75</t>
@@ -185,8 +210,8 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -527,21 +552,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="10" customWidth="1"/>
-    <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24" customWidth="1"/>
+    <col min="2" max="2" width="20" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="12" customWidth="1"/>
+    <col min="6" max="6" width="13" style="1" customWidth="1"/>
+    <col min="7" max="7" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
@@ -550,19 +576,25 @@
       <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" sqref="A2:A2000">
       <formula1>Lists!$A$2:$A$4</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" sqref="B2:B2000">
+      <formula1>Lists!$C$2:$C$4</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C2:C2000">
       <formula1>Lists!$B$2:$B$3</formula1>
     </dataValidation>
   </dataValidations>
@@ -574,40 +606,66 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="30" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="D1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -618,7 +676,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
@@ -627,17 +685,17 @@
   <sheetData>
     <row r="1" spans="1:1" s="6" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -645,7 +703,7 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -653,7 +711,7 @@
         <v>1</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -661,7 +719,7 @@
         <v>2</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -669,7 +727,7 @@
         <v>3</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -677,7 +735,7 @@
         <v>4</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -685,7 +743,15 @@
         <v>5</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B11" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
